--- a/workshop_registration_form_templates/031_heart_health_seminar_registration--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/031_heart_health_seminar_registration--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'english',_'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'English', 'value': 'english'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'spanish',_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish', 'value': 'spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'chinese',_'value':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Chinese', 'value': 'chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'lunch',_'value':_'lunch'}</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Lunch', 'value': 'lunch'}</t>
+          <t>Lunch</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'snacks',_'value':_'snacks'}</t>
+          <t>snacks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Snacks', 'value': 'snacks'}</t>
+          <t>Snacks</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'parking',_'value':_'parking'}</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Parking', 'value': 'parking'}</t>
+          <t>Parking</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'heart_health',_'value':_'heart_health'}</t>
+          <t>heart_health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Heart Health', 'value': 'heart_health'}</t>
+          <t>Heart Health</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'nutrition',_'value':_'nutrition'}</t>
+          <t>nutrition</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Nutrition', 'value': 'nutrition'}</t>
+          <t>Nutrition</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'fitness',_'value':_'fitness'}</t>
+          <t>fitness</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Fitness', 'value': 'fitness'}</t>
+          <t>Fitness</t>
         </is>
       </c>
     </row>
